--- a/data/valuebets_database_2025-10-31.xlsx
+++ b/data/valuebets_database_2025-10-31.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,10 +505,8 @@
           <t>31/10 16:30</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F2" t="n">
+        <v>200</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -521,7 +519,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>45961.07275709537</v>
+        <v>45961.07275709491</v>
       </c>
     </row>
     <row r="3">
@@ -550,10 +548,8 @@
           <t>31/10 18:15</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F3" t="n">
+        <v>200</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -566,7 +562,7 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>45961.07275709537</v>
+        <v>45961.07275709491</v>
       </c>
     </row>
     <row r="4">
@@ -595,10 +591,8 @@
           <t>31/10 17:30</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F4" t="n">
+        <v>200</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -611,7 +605,7 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>45961.07275709537</v>
+        <v>45961.07275709491</v>
       </c>
     </row>
     <row r="5">
@@ -640,10 +634,8 @@
           <t>31/10 23:00</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F5" t="n">
+        <v>200</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -656,7 +648,7 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>45961.07275709537</v>
+        <v>45961.07275709491</v>
       </c>
     </row>
     <row r="6">
@@ -685,10 +677,8 @@
           <t>31/10 18:30</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F6" t="n">
+        <v>175</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -701,7 +691,7 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>45961.07275709537</v>
+        <v>45961.07275709491</v>
       </c>
     </row>
     <row r="7">
@@ -730,10 +720,8 @@
           <t>31/10 17:00</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F7" t="n">
+        <v>175</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -746,7 +734,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>45961.07275709537</v>
+        <v>45961.07275709491</v>
       </c>
     </row>
     <row r="8">
@@ -775,10 +763,8 @@
           <t>31/10 02:00</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F8" t="n">
+        <v>200</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -791,7 +777,7 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>45961.07275709537</v>
+        <v>45961.07275709491</v>
       </c>
     </row>
     <row r="9">
@@ -820,10 +806,8 @@
           <t>31/10 20:00</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F9" t="n">
+        <v>200</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -836,7 +820,7 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>45961.07275709537</v>
+        <v>45961.07275709491</v>
       </c>
     </row>
     <row r="10">
@@ -865,10 +849,8 @@
           <t>31/10 17:30</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F10" t="n">
+        <v>175</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -881,7 +863,7 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>45961.07275709537</v>
+        <v>45961.07275709491</v>
       </c>
     </row>
     <row r="11">
@@ -910,10 +892,8 @@
           <t>31/10 18:15</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F11" t="n">
+        <v>175</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -926,7 +906,7 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>45961.07275709537</v>
+        <v>45961.07275709491</v>
       </c>
     </row>
     <row r="12">
@@ -955,10 +935,8 @@
           <t>31/10 18:30</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F12" t="n">
+        <v>175</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -971,7 +949,7 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>45961.07275709537</v>
+        <v>45961.07275709491</v>
       </c>
     </row>
     <row r="13">
@@ -1000,10 +978,8 @@
           <t>01/11 02:00</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F13" t="n">
+        <v>200</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1016,7 +992,7 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>45961.07275709537</v>
+        <v>45961.07275709491</v>
       </c>
     </row>
     <row r="14">
@@ -1045,10 +1021,8 @@
           <t>31/10 02:30</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F14" t="n">
+        <v>175</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1061,7 +1035,7 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>45961.07275709537</v>
+        <v>45961.07275709491</v>
       </c>
     </row>
     <row r="15">
@@ -1090,10 +1064,8 @@
           <t>31/10 18:15</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F15" t="n">
+        <v>150</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1106,7 +1078,7 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>45961.07275709537</v>
+        <v>45961.07275709491</v>
       </c>
     </row>
     <row r="16">
@@ -1135,10 +1107,8 @@
           <t>31/10 18:45</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F16" t="n">
+        <v>150</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1151,7 +1121,7 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>45961.07275709537</v>
+        <v>45961.07275709491</v>
       </c>
     </row>
     <row r="17">
@@ -1180,10 +1150,8 @@
           <t>31/10 18:30</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F17" t="n">
+        <v>150</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1196,7 +1164,7 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>45961.07275709537</v>
+        <v>45961.07275709491</v>
       </c>
     </row>
     <row r="18">
@@ -1225,10 +1193,8 @@
           <t>31/10 17:00</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F18" t="n">
+        <v>150</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1241,7 +1207,7 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>45961.07275709537</v>
+        <v>45961.07275709491</v>
       </c>
     </row>
     <row r="19">
@@ -1270,10 +1236,8 @@
           <t>31/10 16:30</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F19" t="n">
+        <v>140</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1286,7 +1250,7 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>45961.07275709537</v>
+        <v>45961.07275709491</v>
       </c>
     </row>
     <row r="20">
@@ -1315,10 +1279,8 @@
           <t>31/10 16:30</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F20" t="n">
+        <v>150</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1331,7 +1293,7 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>45961.07275709537</v>
+        <v>45961.07275709491</v>
       </c>
     </row>
     <row r="21">
@@ -1360,10 +1322,8 @@
           <t>31/10 17:00</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F21" t="n">
+        <v>140</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1376,7 +1336,7 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>45961.07275709537</v>
+        <v>45961.07275709491</v>
       </c>
     </row>
     <row r="22">
@@ -1405,10 +1365,8 @@
           <t>31/10 18:30</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F22" t="n">
+        <v>140</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1421,7 +1379,7 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>45961.07275709537</v>
+        <v>45961.07275709491</v>
       </c>
     </row>
     <row r="23">
@@ -1450,10 +1408,8 @@
           <t>01/11 14:15</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F23" t="n">
+        <v>150</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1466,7 +1422,7 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>45961.07275709537</v>
+        <v>45961.07275709491</v>
       </c>
     </row>
     <row r="24">
@@ -1495,10 +1451,8 @@
           <t>31/10 18:30</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F24" t="n">
+        <v>140</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1511,7 +1465,7 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>45961.07275709537</v>
+        <v>45961.07275709491</v>
       </c>
     </row>
     <row r="25">
@@ -1540,10 +1494,8 @@
           <t>02/11 15:00</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F25" t="n">
+        <v>125</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1556,7 +1508,7 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>45961.07275709537</v>
+        <v>45961.07275709491</v>
       </c>
     </row>
     <row r="26">
@@ -1585,23 +1537,201 @@
           <t>02/11 16:00</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F26" t="n">
+        <v>125</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>+96,6%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>45961.07275709491</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Djurgården</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Djurgårdens IF – Brynäs IFSuède - Suède SHL</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>01/11 14:15</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>+122%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>45961.13377191205</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Pioneers V</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Pioneers Vorarlberg – Fehervar AV19Autriche - Autriche ICE</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>01/11 15:00</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
         <is>
           <t>125.00</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>1,57%</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>+96,6%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="n">
-        <v>45961.07275709537</v>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>1,66%</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>+108%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>45961.13377191205</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Lukko Raum</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Lukko Rauma – Vaasan SportLiiga</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>31/10 16:30</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>125.00</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>1,53%</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>+91,5%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>45961.13377191205</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Sparta Pra</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Sparta Prague – Mlada BoleslavRép. Tchèque - Rép. Tchèque Extraliga</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>02/11 15:00</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>125.00</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>1,51%</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>+88,8%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>45961.13377191205</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-10-31.xlsx
+++ b/data/valuebets_database_2025-10-31.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1580,10 +1580,8 @@
           <t>01/11 14:15</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F27" t="n">
+        <v>150</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1596,7 +1594,7 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>45961.13377191205</v>
+        <v>45961.13377190972</v>
       </c>
     </row>
     <row r="28">
@@ -1625,10 +1623,8 @@
           <t>01/11 15:00</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F28" t="n">
+        <v>125</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1641,7 +1637,7 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>45961.13377191205</v>
+        <v>45961.13377190972</v>
       </c>
     </row>
     <row r="29">
@@ -1670,10 +1666,8 @@
           <t>31/10 16:30</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F29" t="n">
+        <v>125</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1686,7 +1680,7 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>45961.13377191205</v>
+        <v>45961.13377190972</v>
       </c>
     </row>
     <row r="30">
@@ -1715,23 +1709,111 @@
           <t>02/11 15:00</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F30" t="n">
+        <v>125</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>1,51%</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>+88,8%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>45961.13377190972</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Iserlohn –</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Iserlohn – Grizzlys WolfsburgDEL</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>01/11 17:00</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
         <is>
           <t>125.00</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>1,51%</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>+88,8%</t>
         </is>
       </c>
-      <c r="I30" s="2" t="n">
-        <v>45961.13377191205</v>
+      <c r="I31" s="2" t="n">
+        <v>45961.18548089655</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Hockey | Pas de buts | HC Lugano </t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>HC Lugano – Genève-ServetteNational League A</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>01/11 18:45</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>110.00</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>1,71%</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>+87,7%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>45961.18548089655</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-10-31.xlsx
+++ b/data/valuebets_database_2025-10-31.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1752,10 +1752,8 @@
           <t>01/11 17:00</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F31" t="n">
+        <v>125</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1768,7 +1766,7 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>45961.18548089655</v>
+        <v>45961.1854808912</v>
       </c>
     </row>
     <row r="32">
@@ -1797,10 +1795,8 @@
           <t>01/11 18:45</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F32" t="n">
+        <v>110</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1813,7 +1809,187 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>45961.18548089655</v>
+        <v>45961.1854808912</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | JYP Jyväsk</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>JYP Jyväskylä – Kärpät OuluFinlande - Finlande Liiga</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>31/10 16:30</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>225.00</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>1,36%</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>+207%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>45961.22394402351</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Poprad – Z</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Poprad – ZilinaSlovaquie - Slovaquie Extraliga</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>31/10 17:00</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>1,42%</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>+114%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>45961.22394402351</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Kometa Brn</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Kometa Brno – Ceske BudejoviceRép. Tchèque - Rép. Tchèque Extraliga - YYUZJR 385076e7</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>02/11 16:00</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>1,49%</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>+109%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>45961.22394402351</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Iserlohn R</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Iserlohn Roosters – Wolfsburg GrizzlyAllemagne - Allemagne DEL</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>01/11 17:00</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>1,44%</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>+102%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>45961.22394402351</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-10-31.xlsx
+++ b/data/valuebets_database_2025-10-31.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1838,10 +1838,8 @@
           <t>31/10 16:30</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>225.00</t>
-        </is>
+      <c r="F33" t="n">
+        <v>225</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1854,7 +1852,7 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>45961.22394402351</v>
+        <v>45961.22394402778</v>
       </c>
     </row>
     <row r="34">
@@ -1883,10 +1881,8 @@
           <t>31/10 17:00</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F34" t="n">
+        <v>150</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1899,7 +1895,7 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>45961.22394402351</v>
+        <v>45961.22394402778</v>
       </c>
     </row>
     <row r="35">
@@ -1928,10 +1924,8 @@
           <t>02/11 16:00</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F35" t="n">
+        <v>140</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1944,7 +1938,7 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>45961.22394402351</v>
+        <v>45961.22394402778</v>
       </c>
     </row>
     <row r="36">
@@ -1973,23 +1967,246 @@
           <t>01/11 17:00</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F36" t="n">
+        <v>140</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>1,44%</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>+102%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>45961.22394402778</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | KAC – Inns</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>KAC – Innsbruck Die HaieAutriche - Autriche ICE</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>31/10 18:15</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>250.00</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>1,36%</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>+239%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>45961.27340488824</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Hockey | Pas de buts | Bolzano – </t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Bolzano – HC PustertalAutriche - Autriche ICE</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>31/10 18:45</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>1,44%</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>+152%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>45961.27340488824</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Nurnberg I</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Nurnberg Ice Tigers – Straubing TigersAllemagne - Allemagne DEL</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>31/10 18:30</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>1,33%</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>+133%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>45961.27340488824</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Tappara Ta</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Tappara Tampere – HIFKFinlande - Finlande Liiga</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>31/10 16:30</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>1,33%</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>+133%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>45961.27340488824</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Schwenning</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Schwenninger Wild Wings – Eisbären BerlinAllemagne - Allemagne DEL</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>31/10 18:30</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
         <is>
           <t>140.00</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>1,44%</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>+102%</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="n">
-        <v>45961.22394402351</v>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>1,35%</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>+88,9%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>45961.27340488824</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-10-31.xlsx
+++ b/data/valuebets_database_2025-10-31.xlsx
@@ -2010,10 +2010,8 @@
           <t>31/10 18:15</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>250.00</t>
-        </is>
+      <c r="F37" t="n">
+        <v>250</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -2026,7 +2024,7 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>45961.27340488824</v>
+        <v>45961.27340488426</v>
       </c>
     </row>
     <row r="38">
@@ -2055,10 +2053,8 @@
           <t>31/10 18:45</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F38" t="n">
+        <v>175</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2071,7 +2067,7 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>45961.27340488824</v>
+        <v>45961.27340488426</v>
       </c>
     </row>
     <row r="39">
@@ -2100,10 +2096,8 @@
           <t>31/10 18:30</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F39" t="n">
+        <v>175</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -2116,7 +2110,7 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>45961.27340488824</v>
+        <v>45961.27340488426</v>
       </c>
     </row>
     <row r="40">
@@ -2145,10 +2139,8 @@
           <t>31/10 16:30</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F40" t="n">
+        <v>175</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2161,7 +2153,7 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>45961.27340488824</v>
+        <v>45961.27340488426</v>
       </c>
     </row>
     <row r="41">
@@ -2190,10 +2182,8 @@
           <t>31/10 18:30</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F41" t="n">
+        <v>140</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2206,7 +2196,7 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>45961.27340488824</v>
+        <v>45961.27340488426</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-10-31.xlsx
+++ b/data/valuebets_database_2025-10-31.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:I44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2199,6 +2199,141 @@
         <v>45961.27340488426</v>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | FTC-Teleko</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>FTC-Telekom – Graz 99ersAutriche - Autriche ICE</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>31/10 17:30</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>+181%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>45961.3918334362</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Black Wing</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Black Wings Linz – Vienne CapitalsAutriche - Autriche ICE</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>31/10 18:15</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>1,42%</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>+148%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>45961.3918334362</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Moins que 0.5 | EHC Biel-B</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>EHC Biel-Bienne – BernSuisse - Suisse NLA</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Moins que 0.5</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>31/10 18:45</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>85.00</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2,19%</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>+86,0%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>45961.3918334362</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-10-31.xlsx
+++ b/data/valuebets_database_2025-10-31.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I44"/>
+  <dimension ref="A1:I48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2225,10 +2225,8 @@
           <t>31/10 17:30</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F42" t="n">
+        <v>200</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2241,7 +2239,7 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>45961.3918334362</v>
+        <v>45961.3918334375</v>
       </c>
     </row>
     <row r="43">
@@ -2270,10 +2268,8 @@
           <t>31/10 18:15</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F43" t="n">
+        <v>175</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2286,7 +2282,7 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>45961.3918334362</v>
+        <v>45961.3918334375</v>
       </c>
     </row>
     <row r="44">
@@ -2315,10 +2311,8 @@
           <t>31/10 18:45</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>85.00</t>
-        </is>
+      <c r="F44" t="n">
+        <v>85</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2331,7 +2325,187 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>45961.3918334362</v>
+        <v>45961.3918334375</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Davos – Ra</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Davos – Rapperswil Jona LakersSuisse - Suisse NLA</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>01/11 18:45</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>1,54%</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>+169%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>45961.43307514661</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Hockey | Pas de buts | Salzbourg </t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Salzbourg – Olimpija LjubljanaAutriche - Autriche ICE</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>31/10 18:15</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>+147%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>45961.43307514661</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Winamax(FR)Tennis | Plus que 25.5 | Q.Halys / </t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Q.Halys / P-H.Herbert – M.Gonzalez / A.MolteniATP - Open de Paris, Doubles</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Plus que 25.5</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>31/10 13:00</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>6.75</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>33,1%</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>+123%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>45961.43307514661</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | HC Ambri P</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>HC Ambri Piotta – EHC BielNational League A</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>01/11 18:45</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>1,53%</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>+114%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>45961.43307514661</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-10-31.xlsx
+++ b/data/valuebets_database_2025-10-31.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I48"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2354,10 +2354,8 @@
           <t>01/11 18:45</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F45" t="n">
+        <v>175</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2370,7 +2368,7 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>45961.43307514661</v>
+        <v>45961.43307515046</v>
       </c>
     </row>
     <row r="46">
@@ -2399,10 +2397,8 @@
           <t>31/10 18:15</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F46" t="n">
+        <v>175</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2415,7 +2411,7 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>45961.43307514661</v>
+        <v>45961.43307515046</v>
       </c>
     </row>
     <row r="47">
@@ -2444,10 +2440,8 @@
           <t>31/10 13:00</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>6.75</t>
-        </is>
+      <c r="F47" t="n">
+        <v>6.75</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2460,7 +2454,7 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>45961.43307514661</v>
+        <v>45961.43307515046</v>
       </c>
     </row>
     <row r="48">
@@ -2489,23 +2483,66 @@
           <t>01/11 18:45</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="F48" t="n">
+        <v>140</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>1,53%</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>+114%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>45961.43307515046</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Ambri Piot</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ambri Piotta – EHC Biel-BienneSuisse - Suisse NLA</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>01/11 18:45</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
         <is>
           <t>140.00</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>1,53%</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>+114%</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="n">
-        <v>45961.43307514661</v>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>1,59%</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>+122%</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>45961.47113235544</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-10-31.xlsx
+++ b/data/valuebets_database_2025-10-31.xlsx
@@ -2526,10 +2526,8 @@
           <t>01/11 18:45</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F49" t="n">
+        <v>140</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2542,7 +2540,7 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>45961.47113235544</v>
+        <v>45961.47113236111</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-10-31.xlsx
+++ b/data/valuebets_database_2025-10-31.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:I50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2543,6 +2543,51 @@
         <v>45961.47113236111</v>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Munich – A</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Munich – Adler MannheimAllemagne - Allemagne DEL</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>31/10 18:30</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>1,38%</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>+107%</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>45961.59880290247</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-10-31.xlsx
+++ b/data/valuebets_database_2025-10-31.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:I56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2569,23 +2569,291 @@
           <t>31/10 18:30</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="F50" t="n">
+        <v>150</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>1,38%</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>+107%</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>45961.59880290509</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Columbus B</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Columbus Blue Jackets – St. Louis BluesNHL</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>01/11 23:00</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>1,37%</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>+173%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>45961.64004621004</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Boston Bru</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Boston Bruins – Carolina HurricanesNHL</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>01/11 17:00</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>1,36%</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>+173%</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>45961.64004621004</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Philadelph</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Philadelphia Flyers – Toronto Maple LeafsNHL</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>01/11 23:00</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>1,27%</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>+154%</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>45961.64004621004</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Edmonton O</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Edmonton Oilers – Chicago BlackhawksNHL</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>02/11 02:00</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>1,24%</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>+149%</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>45961.64004621004</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | HC Davos –</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>HC Davos – SC Rapperswil-Jona LakersNational League A</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>01/11 18:45</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
         <is>
           <t>150.00</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>1,38%</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>+107%</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="n">
-        <v>45961.59880290247</v>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>+133%</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>45961.64004621004</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Seattle Kr</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Seattle Kraken – NY RangersNHL</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>02/11 02:00</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>1,31%</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>+129%</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>45961.64004621004</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-10-31.xlsx
+++ b/data/valuebets_database_2025-10-31.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I56"/>
+  <dimension ref="A1:I63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2612,10 +2612,8 @@
           <t>01/11 23:00</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F51" t="n">
+        <v>200</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2628,7 +2626,7 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>45961.64004621004</v>
+        <v>45961.64004621527</v>
       </c>
     </row>
     <row r="52">
@@ -2657,10 +2655,8 @@
           <t>01/11 17:00</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F52" t="n">
+        <v>200</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2673,7 +2669,7 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>45961.64004621004</v>
+        <v>45961.64004621527</v>
       </c>
     </row>
     <row r="53">
@@ -2702,10 +2698,8 @@
           <t>01/11 23:00</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F53" t="n">
+        <v>200</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2718,7 +2712,7 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>45961.64004621004</v>
+        <v>45961.64004621527</v>
       </c>
     </row>
     <row r="54">
@@ -2747,10 +2741,8 @@
           <t>02/11 02:00</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F54" t="n">
+        <v>200</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2763,7 +2755,7 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>45961.64004621004</v>
+        <v>45961.64004621527</v>
       </c>
     </row>
     <row r="55">
@@ -2792,10 +2784,8 @@
           <t>01/11 18:45</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F55" t="n">
+        <v>150</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2808,7 +2798,7 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>45961.64004621004</v>
+        <v>45961.64004621527</v>
       </c>
     </row>
     <row r="56">
@@ -2837,23 +2827,336 @@
           <t>02/11 02:00</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="F56" t="n">
+        <v>175</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>1,31%</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>+129%</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>45961.64004621527</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Olimpija L</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Olimpija Ljubljana – Innsbruck Die HaieAutriche - Autriche ICE</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>01/11 17:00</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>375.00</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>1,24%</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>+366%</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>45961.68629111883</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Montreal C</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Montreal Canadiens – Ottawa SenatorsNHL</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>01/11 23:00</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>1,36%</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>+173%</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>45961.68629111883</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Winnipeg J</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Winnipeg Jets – Pittsburgh PenguinsNHL</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>01/11 19:00</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>1,36%</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>+172%</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>45961.68629111883</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Hockey | Pas de buts | Minnesota </t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Minnesota Wild – Vancouver CanucksNHL</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>01/11 23:00</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>1,33%</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>+165%</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>45961.68629111883</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Buffalo Sa</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Buffalo Sabres – Washington CapitalsNHL</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>01/11 23:00</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>1,32%</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>+164%</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>45961.68629111883</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Florida Pa</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Florida Panthers – Dallas StarsNHL</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>01/11 22:00</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
         <is>
           <t>175.00</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>1,31%</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>+129%</t>
-        </is>
-      </c>
-      <c r="I56" s="2" t="n">
-        <v>45961.64004621004</v>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>1,37%</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>+139%</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>45961.68629111883</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Hockey | Pas de buts | Nashville </t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Nashville Predators – Calgary FlamesNHL</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>01/11 19:30</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>1,36%</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>+138%</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>45961.68629111883</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-10-31.xlsx
+++ b/data/valuebets_database_2025-10-31.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I63"/>
+  <dimension ref="A1:I64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2870,10 +2870,8 @@
           <t>01/11 17:00</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>375.00</t>
-        </is>
+      <c r="F57" t="n">
+        <v>375</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2886,7 +2884,7 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>45961.68629111883</v>
+        <v>45961.68629112269</v>
       </c>
     </row>
     <row r="58">
@@ -2915,10 +2913,8 @@
           <t>01/11 23:00</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F58" t="n">
+        <v>200</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2931,7 +2927,7 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>45961.68629111883</v>
+        <v>45961.68629112269</v>
       </c>
     </row>
     <row r="59">
@@ -2960,10 +2956,8 @@
           <t>01/11 19:00</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F59" t="n">
+        <v>200</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2976,7 +2970,7 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>45961.68629111883</v>
+        <v>45961.68629112269</v>
       </c>
     </row>
     <row r="60">
@@ -3005,10 +2999,8 @@
           <t>01/11 23:00</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F60" t="n">
+        <v>200</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -3021,7 +3013,7 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>45961.68629111883</v>
+        <v>45961.68629112269</v>
       </c>
     </row>
     <row r="61">
@@ -3050,10 +3042,8 @@
           <t>01/11 23:00</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F61" t="n">
+        <v>200</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -3066,7 +3056,7 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>45961.68629111883</v>
+        <v>45961.68629112269</v>
       </c>
     </row>
     <row r="62">
@@ -3095,10 +3085,8 @@
           <t>01/11 22:00</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F62" t="n">
+        <v>175</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -3111,7 +3099,7 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>45961.68629111883</v>
+        <v>45961.68629112269</v>
       </c>
     </row>
     <row r="63">
@@ -3140,10 +3128,8 @@
           <t>01/11 19:30</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F63" t="n">
+        <v>175</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -3156,7 +3142,52 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>45961.68629111883</v>
+        <v>45961.68629112269</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Ingolstadt</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Ingolstadt – Kölner HaieAllemagne - Allemagne DEL</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>31/10 18:30</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>1,35%</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>+169%</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>45961.72232688312</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-10-31.xlsx
+++ b/data/valuebets_database_2025-10-31.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I64"/>
+  <dimension ref="A1:I66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3171,23 +3171,111 @@
           <t>31/10 18:30</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="F64" t="n">
+        <v>200</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>1,35%</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>+169%</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>45961.72232688657</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Olimpija L</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Olimpija Ljubljana – HC Twk Innsbruck Die HaieICE</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>01/11 17:00</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
         <is>
           <t>200.00</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="G65" t="inlineStr">
         <is>
           <t>1,35%</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>+169%</t>
-        </is>
-      </c>
-      <c r="I64" s="2" t="n">
-        <v>45961.72232688312</v>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>+171%</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>45961.77239581684</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Hockey | Pas de buts | Orebro HK </t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Orebro HK – Skelleftea AIKSHL</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>01/11 17:00</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>110.00</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>1,65%</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>+81,8%</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>45961.77239581684</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-10-31.xlsx
+++ b/data/valuebets_database_2025-10-31.xlsx
@@ -3214,10 +3214,8 @@
           <t>01/11 17:00</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F65" t="n">
+        <v>200</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -3230,7 +3228,7 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>45961.77239581684</v>
+        <v>45961.77239582176</v>
       </c>
     </row>
     <row r="66">
@@ -3259,10 +3257,8 @@
           <t>01/11 17:00</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F66" t="n">
+        <v>110</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -3275,7 +3271,7 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>45961.77239581684</v>
+        <v>45961.77239582176</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-10-31.xlsx
+++ b/data/valuebets_database_2025-10-31.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I66"/>
+  <dimension ref="A1:I71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3274,6 +3274,231 @@
         <v>45961.77239582176</v>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | KooKoo – J</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>KooKoo – JYP Jyvaskyla385076e7 Liiga</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>01/11 15:00</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>+179%</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="n">
+        <v>45961.85064247162</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Vienne Cap</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Vienne Capitals – EC VSVAutriche - Autriche ICE</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>02/11 16:30</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>1,34%</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>+168%</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="n">
+        <v>45961.85064247162</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Vaasan Spo</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Vaasan Sport – Lukko RaumaLiiga</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>01/11 13:00</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>+146%</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="n">
+        <v>45961.85064247162</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Berlin – F</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Berlin – Fischtown PinguinsDEL</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>02/11 15:30</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>1,30%</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>+95,5%</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="n">
+        <v>45961.85064247162</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Kärpät Oul</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Kärpät Oulu – Tappara TampereLiiga</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>01/11 15:00</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>125.00</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>1,49%</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>+86,2%</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="n">
+        <v>45961.85064247162</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-10-31.xlsx
+++ b/data/valuebets_database_2025-10-31.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I71"/>
+  <dimension ref="A1:I76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3300,10 +3300,8 @@
           <t>01/11 15:00</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F67" t="n">
+        <v>200</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -3316,7 +3314,7 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>45961.85064247162</v>
+        <v>45961.85064247685</v>
       </c>
     </row>
     <row r="68">
@@ -3345,10 +3343,8 @@
           <t>02/11 16:30</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F68" t="n">
+        <v>200</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -3361,7 +3357,7 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>45961.85064247162</v>
+        <v>45961.85064247685</v>
       </c>
     </row>
     <row r="69">
@@ -3390,10 +3386,8 @@
           <t>01/11 13:00</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F69" t="n">
+        <v>175</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -3406,7 +3400,7 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>45961.85064247162</v>
+        <v>45961.85064247685</v>
       </c>
     </row>
     <row r="70">
@@ -3435,10 +3429,8 @@
           <t>02/11 15:30</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F70" t="n">
+        <v>150</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -3451,7 +3443,7 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>45961.85064247162</v>
+        <v>45961.85064247685</v>
       </c>
     </row>
     <row r="71">
@@ -3480,10 +3472,8 @@
           <t>01/11 15:00</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F71" t="n">
+        <v>125</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -3496,7 +3486,232 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>45961.85064247162</v>
+        <v>45961.85064247685</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Spusu Vien</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Spusu Vienna Capitals – EC Villacher SVICE</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>02/11 16:30</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>1,51%</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>+202%</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="n">
+        <v>45961.88751675668</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Hockey | Pas de buts | Liptovsky </t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Liptovsky Mikulas – PresovSlovaquie - Slovaquie Extraliga</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>02/11 16:00</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>1,43%</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>+150%</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="n">
+        <v>45961.88751675668</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Kosice – N</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Kosice – NitraSlovaquie - Slovaquie Extraliga</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>02/11 16:30</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>1,46%</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>+119%</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="n">
+        <v>45961.88751675668</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Spisska No</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Spisska Nova Ves – PopradSlovaquie - Slovaquie Extraliga</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>02/11 15:00</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>1,44%</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>+116%</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="n">
+        <v>45961.88751675668</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Dukla Mich</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Dukla Michalovce – HKM AS ZvolenExtraliga</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>02/11 15:30</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>1,40%</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>+111%</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="n">
+        <v>45961.88751675668</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-10-31.xlsx
+++ b/data/valuebets_database_2025-10-31.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I76"/>
+  <dimension ref="A1:I80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3515,10 +3515,8 @@
           <t>02/11 16:30</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F72" t="n">
+        <v>200</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -3531,7 +3529,7 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>45961.88751675668</v>
+        <v>45961.88751675926</v>
       </c>
     </row>
     <row r="73">
@@ -3560,10 +3558,8 @@
           <t>02/11 16:00</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F73" t="n">
+        <v>175</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -3576,7 +3572,7 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>45961.88751675668</v>
+        <v>45961.88751675926</v>
       </c>
     </row>
     <row r="74">
@@ -3605,10 +3601,8 @@
           <t>02/11 16:30</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F74" t="n">
+        <v>150</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -3621,7 +3615,7 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>45961.88751675668</v>
+        <v>45961.88751675926</v>
       </c>
     </row>
     <row r="75">
@@ -3650,10 +3644,8 @@
           <t>02/11 15:00</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F75" t="n">
+        <v>150</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -3666,7 +3658,7 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>45961.88751675668</v>
+        <v>45961.88751675926</v>
       </c>
     </row>
     <row r="76">
@@ -3695,10 +3687,8 @@
           <t>02/11 15:30</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F76" t="n">
+        <v>150</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -3711,7 +3701,187 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>45961.88751675668</v>
+        <v>45961.88751675926</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Slovan Bra</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Slovan Bratislava – Banska BystricaSlovaquie - Slovaquie Extraliga</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>02/11 15:00</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>1,35%</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>+170%</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="n">
+        <v>45961.93091826014</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Michalovce</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Michalovce – ZvolenSlovaquie - Slovaquie Extraliga</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>02/11 15:30</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>1,40%</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>+145%</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="n">
+        <v>45961.93091826014</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Mhk 32 Lip</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Mhk 32 Liptovsky Mikulas – HC PresovExtraliga</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>02/11 16:00</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>1,36%</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>+138%</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="n">
+        <v>45961.93091826014</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Eisbären B</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Eisbären Berlin – Fischtown PinguinsAllemagne - Allemagne DEL</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>02/11 15:30</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>1,31%</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>+129%</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="n">
+        <v>45961.93091826014</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-10-31.xlsx
+++ b/data/valuebets_database_2025-10-31.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I80"/>
+  <dimension ref="A1:I81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3730,10 +3730,8 @@
           <t>02/11 15:00</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F77" t="n">
+        <v>200</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -3746,7 +3744,7 @@
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>45961.93091826014</v>
+        <v>45961.93091826389</v>
       </c>
     </row>
     <row r="78">
@@ -3775,10 +3773,8 @@
           <t>02/11 15:30</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F78" t="n">
+        <v>175</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -3791,7 +3787,7 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>45961.93091826014</v>
+        <v>45961.93091826389</v>
       </c>
     </row>
     <row r="79">
@@ -3820,10 +3816,8 @@
           <t>02/11 16:00</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F79" t="n">
+        <v>175</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -3836,7 +3830,7 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>45961.93091826014</v>
+        <v>45961.93091826389</v>
       </c>
     </row>
     <row r="80">
@@ -3865,10 +3859,8 @@
           <t>02/11 15:30</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F80" t="n">
+        <v>175</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -3881,7 +3873,52 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>45961.93091826014</v>
+        <v>45961.93091826389</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | KooKoo – J</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>KooKoo – JYP JyväskyläFinlande - Finlande Liiga</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>01/11 15:00</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>225.00</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>1,32%</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>+197%</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="n">
+        <v>45961.97210855073</v>
       </c>
     </row>
   </sheetData>
